--- a/qupath-nk-vessel-analysis/Prism_ready_analysis.xlsx
+++ b/qupath-nk-vessel-analysis/Prism_ready_analysis.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README_Analyseplan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="A1_NKdensity_IB4" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="A1_NKdensity_Syn" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="A2_Perivascular_pct" sheetId="4" state="visible" r:id="rId4"/>
@@ -15,8 +15,9 @@
     <sheet name="A4_Dist_to_Syn" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="A5_Caliber_NKwithin20" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="A6_Activation_by_location" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="AnimalLevel_means" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="PerImage_tidy" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="A7_Perivasc_NK_vs_background" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="A8_DistSyn_NK_vs_background" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="AnimalLevel_means" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,248 +438,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NK-Zell / Gefäß / Nerv – Analyseplan &amp; Prism-Tabellen</t>
+          <t>Prism-fertige Tabellen – welches Sheet in welche Prism-Analyse</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jeder Block: Kopfzeile = Gruppen, darunter je Bild ein Wert. In Prism einfuegen.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Design (aus Dateinamen dekodiert):</t>
+          <t>BIOL. REPLIKAT = TIER (hier n=2) -&gt; p-Werte deskriptiv/Pilot! AnimalLevel_means zeigt Tiermittel.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Tiere (biol. Replikat): 2  — 86426 (m), 89807 (f).  Genotyp: nur WT.</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Bedingung: OP (operiert) vs N (naiv/kontralateral) — beide Tiere haben beide Seiten.</t>
+          <t>A1_NKdensity_*  : NK-Dichte OP vs N (je Panel)        -&gt; Mann-Whitney</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Panel: IB4 (Gefäße: small/large) vs Synaptophysin (Nerventerminals/NMJ) – SEPARATE Schnitte.</t>
+          <t>A2_Perivascular : % NK &lt;20µm am Gefaess, OP vs N       -&gt; Mann-Whitney</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ~3 Bilder je Schnitt; Kontroll-/Negativbilder (NK=0) ausgeschlossen.</t>
+          <t>A3_Dist_small_vs_large : gepaart je IB4-Bild           -&gt; Wilcoxon paired</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A4_Dist_to_Syn  : NK-&gt;Synaptophysin OP vs N            -&gt; Mann-Whitney</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>*** WICHTIGSTER STAT-HINWEIS ***</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A5_Caliber_NKwithin20 : small vs large, gepaart        -&gt; Wilcoxon paired</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Biologisches Replikat = TIER, nicht Bild und nicht Zelle. Hier n=2 Tiere.</t>
+          <t>A6_Activation_by_location : NKp46/Flaeche peri vs nicht -&gt; Wilcoxon paired</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  =&gt; Mit n=2 sind p-Werte über Tiere NICHT belastbar (rein deskriptiv / Pilot).</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>A7_Perivasc_NK_vs_background : NK vs Nicht-NK, gepaart  -&gt; Wilcoxon paired (ANREICHERUNG)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  =&gt; Zellen/Bilder als 'n' zu verwenden ist Pseudoreplikation (Lazic 2010; Aarts 2014).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Empfehlung: Pilot beschreiben (Effektgrößen + Einzeltierpunkte zeigen);</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  für Inferenz n&gt;=4-5 Tiere/Gruppe sammeln und gemischte Modelle (Bild in Tier genestet) nutzen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Vorgeschlagene Analysen (Sheet -&gt; Prism-Test):</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A1  NK-Dichte OP vs N (IB4 &amp; Syn getrennt) -&gt; Mann-Whitney / ungepaart; Tier-Mittel paarweise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A2  Perivaskulärer Anteil % (NK &lt;20µm an Gefäß) OP vs N -&gt; Mann-Whitney.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A3  Distanz NK-&gt;small vs -&gt;large Gefäß (gepaart je IB4-Bild) -&gt; Wilcoxon paired.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A4  Distanz NK-&gt;Synaptophysin OP vs N -&gt; Mann-Whitney.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A5  NK im 20µm-Umkreis je Gefäß: small vs large Kaliber -&gt; Mann-Whitney/paired je Bild.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A6  Aktivierung nach Lage: NKp46-Intensität &amp; Zellfläche perivaskulär vs nicht (gepaart je Bild) -&gt; Wilcoxon paired.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>WICHTIG – Anreicherungstest fehlt noch (empfohlen!):</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Um zu zeigen, dass NK-Zellen NÄHER an Gefäßen/Nerven liegen als zufällig,</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  vergleiche NK- gegen Nicht-NK-Zell-Distanzen in DENSELBEN Schnitten</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (oder gegen permutierte Zufallspositionen / Ripley-K).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Der aktuelle Export enthält nur NK-Distanzen. Ich kann das QuPath-Skript erweitern,</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  sodass es auch die Nicht-NK-Hintergrunddistanzen exportiert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Referenzen (real, bitte domänenspezifische selbst gegenprüfen):</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Spatial point patterns: Ripley BD 1977 JRSS-B; Baddeley/Rubak/Turner 2015 (spatstat-Buch); Diggle 2013.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Nachbarschafts-/Anreicherungstests in Gewebe-Imaging: Schapiro 2017 (histoCAT) Nat Methods;</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Palla 2022 (squidpy) Nat Methods; Windhager 2023 (imcRtools/steinbock) Nat Protocols.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  QuPath-Methodik: Bankhead 2017 Sci Rep.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Pseudoreplikation/genestete Daten: Lazic 2010 BMC Neurosci; Aarts 2014 Nat Neurosci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Immunzellen im Muskel (Kontext): Tidball 2017 Nat Rev Immunol.</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>A8_DistSyn_NK_vs_background  : NK vs Nicht-NK, gepaart  -&gt; Wilcoxon paired (ANREICHERUNG)</t>
         </is>
       </c>
     </row>
@@ -693,1732 +535,520 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>animal</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>sex</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ANREICHERUNG: NK vs Nicht-NK Distanz-&gt;Synaptophysin, gepaart je Syn-Bild. Wilcoxon paired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>cond</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>panel</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>NK_count</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>NK_density_per_mm2</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>vessel_area_fraction_pct</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>perivascular_pct</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>mean_dist_small_um</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>mean_dist_large_um</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>mean_dist_syn_um</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MAX_gcN_WT_86426_m_2.2_NKp46_IB4 1 - Artefakte.tif</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.325</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.513</v>
-      </c>
-      <c r="J2" t="n">
-        <v>88.235</v>
-      </c>
-      <c r="K2" t="n">
-        <v>10.992</v>
-      </c>
-      <c r="L2" t="n">
-        <v>11.861</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MAX_gcN_WT_86426_m_2.2_NKp46_IB4 2 - ok.tif</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>67</v>
-      </c>
-      <c r="H3" t="n">
-        <v>123.459</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.675</v>
-      </c>
-      <c r="J3" t="n">
-        <v>97.015</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11.749</v>
-      </c>
-      <c r="L3" t="n">
-        <v>11.047</v>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>NK_dist_syn</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>nonNK_dist_syn</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MAX_gcN_WT_86426_m_2.2_NKp46_IB4 3 - ok + Artefakt.tif</t>
+          <t>MAX_gcN_WT_86426_m_2.2_NKp46_Syn 1 - not</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H4" t="n">
-        <v>58.914</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.043</v>
-      </c>
-      <c r="J4" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>9.004</v>
-      </c>
-      <c r="L4" t="n">
-        <v>29.924</v>
+      <c r="C4" t="n">
+        <v>31.472</v>
+      </c>
+      <c r="D4" t="n">
+        <v>56.233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MAX_gcN_WT_86426_m_2.2_NKp46_Syn 1 - not good.tif</t>
+          <t>MAX_gcN_WT_86426_m_2.2_NKp46_Syn 2 - sch</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H5" t="n">
-        <v>36.822</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>31.472</v>
+      <c r="C5" t="n">
+        <v>44.883</v>
+      </c>
+      <c r="D5" t="n">
+        <v>70.377</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAX_gcN_WT_86426_m_2.2_NKp46_Syn 2 - schwach.tif</t>
+          <t xml:space="preserve">MAX_gcN_WT_86426_m_2.2_NKp46_Syn 3 - ok </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>182</v>
-      </c>
-      <c r="H6" t="n">
-        <v>335.193</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>44.883</v>
+      <c r="C6" t="n">
+        <v>33.419</v>
+      </c>
+      <c r="D6" t="n">
+        <v>40.191</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MAX_gcN_WT_86426_m_2.2_NKp46_Syn 3 - ok zentral.tif</t>
+          <t xml:space="preserve">MAX_gcOP_WT_86426_m_1.1_NKp46_Syn 1_new </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>88</v>
-      </c>
-      <c r="H7" t="n">
-        <v>162.155</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>33.419</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5.499</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12.901</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_1.1_NKp46_IB4 1_new - gut_tile_problem.tif</t>
+          <t xml:space="preserve">MAX_gcOP_WT_86426_m_1.1_NKp46_Syn 2_new </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>197</v>
-      </c>
-      <c r="H8" t="n">
-        <v>461.014</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6.171</v>
-      </c>
-      <c r="J8" t="n">
-        <v>94.416</v>
-      </c>
-      <c r="K8" t="n">
-        <v>12.149</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7.303</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>23.652</v>
+      </c>
+      <c r="D8" t="n">
+        <v>27.836</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_1.1_NKp46_IB4 2_new - ok_tiles.tif</t>
+          <t xml:space="preserve">MAX_gcOP_WT_86426_m_1.1_NKp46_Syn 3_new </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>153</v>
-      </c>
-      <c r="H9" t="n">
-        <v>281.783</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5.337</v>
-      </c>
-      <c r="J9" t="n">
-        <v>81.04600000000001</v>
-      </c>
-      <c r="K9" t="n">
-        <v>14.323</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9.904</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>30.854</v>
+      </c>
+      <c r="D9" t="n">
+        <v>39.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_1.1_NKp46_IB4 3_new - ok_tiles.tif</t>
+          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_Syn 1 - go</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>248</v>
-      </c>
-      <c r="H10" t="n">
-        <v>456.746</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9.292999999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>72.17700000000001</v>
-      </c>
-      <c r="K10" t="n">
-        <v>23.269</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10.624</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.923</v>
+      </c>
+      <c r="D10" t="n">
+        <v>19.262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_1.1_NKp46_Syn 1_new - ok.tif</t>
+          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_Syn 2 - go</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>84</v>
-      </c>
-      <c r="H11" t="n">
-        <v>154.784</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5.499</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8.933</v>
+      </c>
+      <c r="D11" t="n">
+        <v>29.109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_1.1_NKp46_Syn 2_new - schwach.tif</t>
+          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_Syn 3 - go</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>116</v>
-      </c>
-      <c r="H12" t="n">
-        <v>213.675</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>23.652</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6.791</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24.956</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_1.1_NKp46_Syn 3_new - sehr gut.tif</t>
+          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_Syn 1 - go</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>545</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1345.174</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>30.854</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>16.732</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20.314</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_IB4 1 - good.tif</t>
+          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_Syn 2_good</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>131</v>
-      </c>
-      <c r="H14" t="n">
-        <v>241.265</v>
-      </c>
-      <c r="I14" t="n">
-        <v>14.423</v>
-      </c>
-      <c r="J14" t="n">
-        <v>100</v>
-      </c>
-      <c r="K14" t="n">
-        <v>28.131</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-2.247</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>29.836</v>
+      </c>
+      <c r="D14" t="n">
+        <v>31.471</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_IB4 2 - ok.tif</t>
+          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_Syn 3 - go</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>177</v>
-      </c>
-      <c r="H15" t="n">
-        <v>326.152</v>
-      </c>
-      <c r="I15" t="n">
-        <v>23.867</v>
-      </c>
-      <c r="J15" t="n">
-        <v>100</v>
-      </c>
-      <c r="K15" t="n">
-        <v>23.728</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-2.489</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>59.102</v>
+      </c>
+      <c r="D15" t="n">
+        <v>73.447</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_IB4 3 - tile problem.tif</t>
+          <t>MAX_gcN_WT_89807_f_2.1_NKp46_Syn 2 - zen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>215</v>
-      </c>
-      <c r="H16" t="n">
-        <v>395.969</v>
-      </c>
-      <c r="I16" t="n">
-        <v>24.358</v>
-      </c>
-      <c r="J16" t="n">
-        <v>99.06999999999999</v>
-      </c>
-      <c r="K16" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.774</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>23.878</v>
+      </c>
+      <c r="D16" t="n">
+        <v>37.489</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_Syn 1 - good.tif</t>
+          <t>done - gcOP_WT_89807_f_5.1_NKp46_Syn 1.t</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>406</v>
-      </c>
-      <c r="H17" t="n">
-        <v>910.25</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5.923</v>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>44.655</v>
+      </c>
+      <c r="D17" t="n">
+        <v>91.583</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_Syn 2 - good.tif</t>
+          <t>done - gcOP_WT_89807_f_5.1_NKp46_Syn 3.t</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>20.908</v>
+      </c>
+      <c r="D18" t="n">
+        <v>29.664</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Tier-Mittel (richtiges biol. Replikat, n=2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>cond</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>NK_density_per_mm2</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>perivascular_pct</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>mean_dist_small_um</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>mean_dist_large_um</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>mean_dist_syn_um</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>nonNK_perivascular_pct</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>nonNK_mean_dist_syn_um</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>86426</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>213</v>
-      </c>
-      <c r="H18" t="n">
-        <v>392.488</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>8.933</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_Syn 3 - good.tif</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>673.4400000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="H4" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="I4" t="n">
+        <v>30.93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>86426</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>396</v>
-      </c>
-      <c r="H19" t="n">
-        <v>729.3200000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.791</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_IB4 1 - good.tif</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>284</v>
-      </c>
-      <c r="H20" t="n">
-        <v>577.194</v>
-      </c>
-      <c r="I20" t="n">
-        <v>22.077</v>
-      </c>
-      <c r="J20" t="n">
-        <v>98.59099999999999</v>
-      </c>
-      <c r="K20" t="n">
-        <v>11.328</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2.273</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_IB4 2 - good.tif</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>259</v>
-      </c>
-      <c r="H21" t="n">
-        <v>565.6180000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5.718</v>
-      </c>
-      <c r="J21" t="n">
-        <v>92.27800000000001</v>
-      </c>
-      <c r="K21" t="n">
-        <v>8.523</v>
-      </c>
-      <c r="L21" t="n">
-        <v>11.243</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_IB4 3 - good.tif</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>281</v>
-      </c>
-      <c r="H22" t="n">
-        <v>517.789</v>
-      </c>
-      <c r="I22" t="n">
-        <v>16.076</v>
-      </c>
-      <c r="J22" t="n">
-        <v>100</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.498</v>
-      </c>
-      <c r="L22" t="n">
-        <v>4.682</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_Syn 1 - good.tif</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>583</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1351.295</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>16.732</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_Syn 2_good.tif</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>832</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1997.642</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>29.836</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_Syn 3 - good_tile.tif</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>86426</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>523</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1203.788</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>59.102</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MAX_gcN_WT_89807_f_2.1_NKp46_IB4 1 - kaum NKp.tif</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>124.64</v>
+      </c>
+      <c r="D5" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="G5" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="H5" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="I5" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>89807</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>471.96</v>
+      </c>
+      <c r="D6" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="G6" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="H6" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="I6" t="n">
+        <v>60.62</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>89807</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>52</v>
-      </c>
-      <c r="H26" t="n">
-        <v>95.736</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3.539</v>
-      </c>
-      <c r="J26" t="n">
-        <v>92.30800000000001</v>
-      </c>
-      <c r="K26" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="L26" t="n">
-        <v>21.849</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MAX_gcN_WT_89807_f_2.1_NKp46_IB4 2 - kaum NKp.tif</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>89807</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>93</v>
-      </c>
-      <c r="H27" t="n">
-        <v>171.22</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.865</v>
-      </c>
-      <c r="J27" t="n">
-        <v>39.785</v>
-      </c>
-      <c r="K27" t="n">
-        <v>22.058</v>
-      </c>
-      <c r="L27" t="n">
-        <v>36.526</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>MAX_gcN_WT_89807_f_2.1_NKp46_IB4 3 - kaum  NKp.tif</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>89807</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>49</v>
-      </c>
-      <c r="H28" t="n">
-        <v>90.21299999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.567</v>
-      </c>
-      <c r="J28" t="n">
-        <v>97.959</v>
-      </c>
-      <c r="K28" t="n">
-        <v>15.062</v>
-      </c>
-      <c r="L28" t="n">
-        <v>11.536</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MAX_gcN_WT_89807_f_2.1_NKp46_Syn 2 - zentral unten.tif</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>89807</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>80</v>
-      </c>
-      <c r="H29" t="n">
-        <v>147.338</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>23.878</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PrÃ¤sentation? - gcOP_WT_89807_f_5.1_NKp46_IB4 1.tif</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>89807</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>447</v>
-      </c>
-      <c r="H30" t="n">
-        <v>823.249</v>
-      </c>
-      <c r="I30" t="n">
-        <v>11.077</v>
-      </c>
-      <c r="J30" t="n">
-        <v>94.855</v>
-      </c>
-      <c r="K30" t="n">
-        <v>9.856</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5.617</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>done - gcOP_WT_89807_f_5.1_NKp46_IB4 2.tif</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>89807</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>30</v>
-      </c>
-      <c r="H31" t="n">
-        <v>55.261</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.988</v>
-      </c>
-      <c r="J31" t="n">
-        <v>83.333</v>
-      </c>
-      <c r="K31" t="n">
-        <v>10.881</v>
-      </c>
-      <c r="L31" t="n">
-        <v>28.499</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>done - gcOP_WT_89807_f_5.1_NKp46_IB4 3.tif</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>89807</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>125</v>
-      </c>
-      <c r="H32" t="n">
-        <v>230.333</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.618</v>
-      </c>
-      <c r="J32" t="n">
-        <v>64</v>
-      </c>
-      <c r="K32" t="n">
-        <v>15.541</v>
-      </c>
-      <c r="L32" t="n">
-        <v>36.033</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>done - gcOP_WT_89807_f_5.1_NKp46_IB4 4.tif</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>89807</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>IB4</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>57</v>
-      </c>
-      <c r="H33" t="n">
-        <v>105.032</v>
-      </c>
-      <c r="I33" t="n">
-        <v>3.925</v>
-      </c>
-      <c r="J33" t="n">
-        <v>82.456</v>
-      </c>
-      <c r="K33" t="n">
-        <v>7.326</v>
-      </c>
-      <c r="L33" t="n">
-        <v>34.121</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>done - gcOP_WT_89807_f_5.1_NKp46_Syn 1.tif</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>89807</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>510</v>
-      </c>
-      <c r="H34" t="n">
-        <v>939.76</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>44.655</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>done - gcOP_WT_89807_f_5.1_NKp46_Syn 3.tif</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>89807</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>OP</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Syn</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>368</v>
-      </c>
-      <c r="H35" t="n">
-        <v>678.101</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>20.908</v>
+      <c r="C7" t="n">
+        <v>126.13</v>
+      </c>
+      <c r="D7" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="E7" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="H7" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="I7" t="n">
+        <v>37.49</v>
       </c>
     </row>
   </sheetData>
@@ -2442,7 +1072,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>NK-Dichte (Zellen/mm²), Panel IB4, je Bild. Prism: Mann-Whitney (deskriptiv, n=2 Tiere!).</t>
+          <t>NK-Dichte (Zellen/mm²), IB4. Mann-Whitney.</t>
         </is>
       </c>
     </row>
@@ -2460,39 +1090,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>461.01</v>
+        <v>461.014</v>
       </c>
       <c r="B4" t="n">
-        <v>31.33</v>
+        <v>31.325</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>281.78</v>
+        <v>281.783</v>
       </c>
       <c r="B5" t="n">
-        <v>123.46</v>
+        <v>123.459</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>456.75</v>
+        <v>456.746</v>
       </c>
       <c r="B6" t="n">
-        <v>58.91</v>
+        <v>58.914</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>241.27</v>
+        <v>241.265</v>
       </c>
       <c r="B7" t="n">
-        <v>95.73999999999999</v>
+        <v>95.736</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>326.15</v>
+        <v>326.152</v>
       </c>
       <c r="B8" t="n">
         <v>171.22</v>
@@ -2500,45 +1130,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>395.97</v>
+        <v>395.969</v>
       </c>
       <c r="B9" t="n">
-        <v>90.20999999999999</v>
+        <v>90.21299999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>577.1900000000001</v>
+        <v>577.194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>565.62</v>
+        <v>565.6180000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>517.79</v>
+        <v>517.789</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>823.25</v>
+        <v>823.249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55.26</v>
+        <v>55.261</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>230.33</v>
+        <v>230.333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105.03</v>
+        <v>105.032</v>
       </c>
     </row>
   </sheetData>
@@ -2562,7 +1192,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>NK-Dichte (Zellen/mm²), Panel Syn, je Bild. Prism: Mann-Whitney (deskriptiv, n=2 Tiere!).</t>
+          <t>NK-Dichte (Zellen/mm²), Syn. Mann-Whitney.</t>
         </is>
       </c>
     </row>
@@ -2580,26 +1210,26 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>154.78</v>
+        <v>154.784</v>
       </c>
       <c r="B4" t="n">
-        <v>36.82</v>
+        <v>36.822</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>213.67</v>
+        <v>213.675</v>
       </c>
       <c r="B5" t="n">
-        <v>335.19</v>
+        <v>335.193</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1345.17</v>
+        <v>1345.174</v>
       </c>
       <c r="B6" t="n">
-        <v>162.15</v>
+        <v>162.155</v>
       </c>
     </row>
     <row r="7">
@@ -2607,12 +1237,12 @@
         <v>910.25</v>
       </c>
       <c r="B7" t="n">
-        <v>147.34</v>
+        <v>147.338</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>392.49</v>
+        <v>392.488</v>
       </c>
     </row>
     <row r="9">
@@ -2622,17 +1252,17 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1351.29</v>
+        <v>1351.295</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1997.64</v>
+        <v>1997.642</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1203.79</v>
+        <v>1203.788</v>
       </c>
     </row>
     <row r="13">
@@ -2642,7 +1272,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>678.1</v>
+        <v>678.101</v>
       </c>
     </row>
   </sheetData>
@@ -2666,7 +1296,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Perivaskulärer Anteil [% NK &lt;20µm am Gefäß], je IB4-Bild. Prism: Mann-Whitney.</t>
+          <t>% NK &lt;20µm am Gefaess, IB4. Mann-Whitney.</t>
         </is>
       </c>
     </row>
@@ -2684,23 +1314,23 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94.42</v>
+        <v>94.416</v>
       </c>
       <c r="B4" t="n">
-        <v>88.23999999999999</v>
+        <v>88.235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81.05</v>
+        <v>81.04600000000001</v>
       </c>
       <c r="B5" t="n">
-        <v>97.01000000000001</v>
+        <v>97.015</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72.18000000000001</v>
+        <v>72.17700000000001</v>
       </c>
       <c r="B6" t="n">
         <v>87.5</v>
@@ -2711,7 +1341,7 @@
         <v>100</v>
       </c>
       <c r="B7" t="n">
-        <v>92.31</v>
+        <v>92.30800000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2719,7 +1349,7 @@
         <v>100</v>
       </c>
       <c r="B8" t="n">
-        <v>39.78</v>
+        <v>39.785</v>
       </c>
     </row>
     <row r="9">
@@ -2727,17 +1357,17 @@
         <v>99.06999999999999</v>
       </c>
       <c r="B9" t="n">
-        <v>97.95999999999999</v>
+        <v>97.959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98.59</v>
+        <v>98.59099999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>92.28</v>
+        <v>92.27800000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2747,12 +1377,12 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94.84999999999999</v>
+        <v>94.855</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>83.33</v>
+        <v>83.333</v>
       </c>
     </row>
     <row r="15">
@@ -2762,7 +1392,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>82.45999999999999</v>
+        <v>82.456</v>
       </c>
     </row>
   </sheetData>
@@ -2785,7 +1415,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Mittl. Distanz NK-&gt;Gefäß je IB4-Bild, gepaart small vs large. Prism: Wilcoxon paired.</t>
+          <t>Mittl. Distanz NK-&gt;Gefaess, gepaart small vs large je IB4-Bild. Wilcoxon paired.</t>
         </is>
       </c>
     </row>
@@ -2823,10 +1453,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.99</v>
+        <v>10.992</v>
       </c>
       <c r="D4" t="n">
-        <v>11.86</v>
+        <v>11.861</v>
       </c>
     </row>
     <row r="5">
@@ -2841,10 +1471,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.75</v>
+        <v>11.749</v>
       </c>
       <c r="D5" t="n">
-        <v>11.05</v>
+        <v>11.047</v>
       </c>
     </row>
     <row r="6">
@@ -2859,10 +1489,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>9.004</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92</v>
+        <v>29.924</v>
       </c>
     </row>
     <row r="7">
@@ -2877,10 +1507,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.15</v>
+        <v>12.149</v>
       </c>
       <c r="D7" t="n">
-        <v>7.3</v>
+        <v>7.303</v>
       </c>
     </row>
     <row r="8">
@@ -2895,10 +1525,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.32</v>
+        <v>14.323</v>
       </c>
       <c r="D8" t="n">
-        <v>9.9</v>
+        <v>9.904</v>
       </c>
     </row>
     <row r="9">
@@ -2913,10 +1543,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.27</v>
+        <v>23.269</v>
       </c>
       <c r="D9" t="n">
-        <v>10.62</v>
+        <v>10.624</v>
       </c>
     </row>
     <row r="10">
@@ -2931,10 +1561,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28.13</v>
+        <v>28.131</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.25</v>
+        <v>-2.247</v>
       </c>
     </row>
     <row r="11">
@@ -2949,10 +1579,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.73</v>
+        <v>23.728</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.49</v>
+        <v>-2.489</v>
       </c>
     </row>
     <row r="12">
@@ -2970,7 +1600,7 @@
         <v>18.85</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.77</v>
+        <v>-0.774</v>
       </c>
     </row>
     <row r="13">
@@ -2985,10 +1615,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.33</v>
+        <v>11.328</v>
       </c>
       <c r="D13" t="n">
-        <v>2.27</v>
+        <v>2.273</v>
       </c>
     </row>
     <row r="14">
@@ -3003,10 +1633,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.52</v>
+        <v>8.523</v>
       </c>
       <c r="D14" t="n">
-        <v>11.24</v>
+        <v>11.243</v>
       </c>
     </row>
     <row r="15">
@@ -3021,10 +1651,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.5</v>
+        <v>4.498</v>
       </c>
       <c r="D15" t="n">
-        <v>4.68</v>
+        <v>4.682</v>
       </c>
     </row>
     <row r="16">
@@ -3042,7 +1672,7 @@
         <v>9.32</v>
       </c>
       <c r="D16" t="n">
-        <v>21.85</v>
+        <v>21.849</v>
       </c>
     </row>
     <row r="17">
@@ -3057,10 +1687,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.06</v>
+        <v>22.058</v>
       </c>
       <c r="D17" t="n">
-        <v>36.53</v>
+        <v>36.526</v>
       </c>
     </row>
     <row r="18">
@@ -3075,16 +1705,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.06</v>
+        <v>15.062</v>
       </c>
       <c r="D18" t="n">
-        <v>11.54</v>
+        <v>11.536</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PrÃ¤sentation? - gcOP_WT_89807_f_5.1_NKp</t>
+          <t>Präsentation? - gcOP_WT_89807_f_5.1_NKp4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3093,10 +1723,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.859999999999999</v>
+        <v>9.856</v>
       </c>
       <c r="D19" t="n">
-        <v>5.62</v>
+        <v>5.617</v>
       </c>
     </row>
     <row r="20">
@@ -3111,10 +1741,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.88</v>
+        <v>10.881</v>
       </c>
       <c r="D20" t="n">
-        <v>28.5</v>
+        <v>28.499</v>
       </c>
     </row>
     <row r="21">
@@ -3129,10 +1759,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15.54</v>
+        <v>15.541</v>
       </c>
       <c r="D21" t="n">
-        <v>36.03</v>
+        <v>36.033</v>
       </c>
     </row>
     <row r="22">
@@ -3147,10 +1777,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7.33</v>
+        <v>7.326</v>
       </c>
       <c r="D22" t="n">
-        <v>34.12</v>
+        <v>34.121</v>
       </c>
     </row>
   </sheetData>
@@ -3174,7 +1804,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Mittl. Distanz NK-&gt;Synaptophysin [µm], je Syn-Bild. Prism: Mann-Whitney.</t>
+          <t>Mittl. Distanz NK-&gt;Synaptophysin [µm], Syn. Mann-Whitney.</t>
         </is>
       </c>
     </row>
@@ -3192,69 +1822,69 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.5</v>
+        <v>5.499</v>
       </c>
       <c r="B4" t="n">
-        <v>31.47</v>
+        <v>31.472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>23.65</v>
+        <v>23.652</v>
       </c>
       <c r="B5" t="n">
-        <v>44.88</v>
+        <v>44.883</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>30.85</v>
+        <v>30.854</v>
       </c>
       <c r="B6" t="n">
-        <v>33.42</v>
+        <v>33.419</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5.92</v>
+        <v>5.923</v>
       </c>
       <c r="B7" t="n">
-        <v>23.88</v>
+        <v>23.878</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8.93</v>
+        <v>8.933</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.79</v>
+        <v>6.791</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16.73</v>
+        <v>16.732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29.84</v>
+        <v>29.836</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>59.1</v>
+        <v>59.102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>44.65</v>
+        <v>44.655</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20.91</v>
+        <v>20.908</v>
       </c>
     </row>
   </sheetData>
@@ -3277,7 +1907,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Mittl. NK-Zahl im 20µm-Umkreis je Gefäß; gepaart small vs large je IB4-Bild. Prism: Wilcoxon paired.</t>
+          <t>Mittl. NK im 20µm-Umkreis je Gefaess; gepaart small vs large. Wilcoxon paired.</t>
         </is>
       </c>
     </row>
@@ -3496,7 +2126,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PrÃ¤sentation? - gcOP_WT_89807_f_5.1_NKp</t>
+          <t>Präsentation? - gcOP_WT_89807_f_5.1_NKp4</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3565,7 +2195,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Pro IB4-Bild: Mittelwert NKp46 (Cell) &amp; Zellfläche, perivaskulär vs nicht. Prism: Wilcoxon paired.</t>
+          <t>Pro IB4-Bild: NKp46 &amp; Zellflaeche, perivaskulaer vs nicht. Wilcoxon paired.</t>
         </is>
       </c>
     </row>
@@ -3892,7 +2522,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PrÃ¤sentation? - gcOP_WT_89807_f_5.1_NKp</t>
+          <t>Präsentation? - gcOP_WT_89807_f_5.1_NKp4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3996,29 +2626,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Tier-Mittelwerte (richtiges biol. Replikat, n=2). Für gepaarte OP-vs-N-Darstellung in Prism.</t>
+          <t>ANREICHERUNG: % perivaskulaer NK vs Nicht-NK, gepaart je IB4-Bild. Wilcoxon paired.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>animal</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -4028,61 +2652,37 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>NK_density_per_mm2</t>
+          <t>NK_perivasc</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>perivascular_pct</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>mean_dist_small_um</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>mean_dist_large_um</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>mean_dist_syn_um</t>
+          <t>nonNK_perivasc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>86426</t>
+          <t>MAX_gcN_WT_86426_m_2.2_NKp46_IB4 1 - Art</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>673.4400000000001</v>
+        <v>88.235</v>
       </c>
       <c r="D4" t="n">
-        <v>46.53</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>20.81</v>
+        <v>43.994</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>86426</t>
+          <t>MAX_gcN_WT_86426_m_2.2_NKp46_IB4 2 - ok.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4091,73 +2691,316 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>124.64</v>
+        <v>97.015</v>
       </c>
       <c r="D5" t="n">
-        <v>45.46</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="F5" t="n">
-        <v>17.61</v>
-      </c>
-      <c r="G5" t="n">
-        <v>36.59</v>
+        <v>35.361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>89807</t>
+          <t xml:space="preserve">MAX_gcN_WT_86426_m_2.2_NKp46_IB4 3 - ok </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>471.96</v>
+        <v>87.5</v>
       </c>
       <c r="D6" t="n">
-        <v>54.11</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="G6" t="n">
-        <v>32.78</v>
+        <v>38.594</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>89807</t>
+          <t xml:space="preserve">MAX_gcOP_WT_86426_m_1.1_NKp46_IB4 1_new </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>94.416</v>
+      </c>
+      <c r="D7" t="n">
+        <v>51.317</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAX_gcOP_WT_86426_m_1.1_NKp46_IB4 2_new </t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>81.04600000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48.268</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAX_gcOP_WT_86426_m_1.1_NKp46_IB4 3_new </t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>72.17700000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>43.601</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_IB4 1 - go</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>67.669</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_IB4 2 - ok</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>80.66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MAX_gcOP_WT_86426_m_2.1_NKp46_IB4 3 - ti</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>80.048</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_IB4 1 - go</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>98.59099999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>82.383</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_IB4 2 - go</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>92.27800000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>53.764</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MAX_gcOP_WT_86426_m_2.2_NKp46_IB4 3 - go</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>96.51000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MAX_gcN_WT_89807_f_2.1_NKp46_IB4 1 - kau</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>126.13</v>
-      </c>
-      <c r="D7" t="n">
-        <v>57.51</v>
-      </c>
-      <c r="E7" t="n">
-        <v>15.48</v>
-      </c>
-      <c r="F7" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>23.88</v>
+      <c r="C16" t="n">
+        <v>92.30800000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MAX_gcN_WT_89807_f_2.1_NKp46_IB4 2 - kau</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>39.785</v>
+      </c>
+      <c r="D17" t="n">
+        <v>23.635</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MAX_gcN_WT_89807_f_2.1_NKp46_IB4 3 - kau</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>97.959</v>
+      </c>
+      <c r="D18" t="n">
+        <v>44.091</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Präsentation? - gcOP_WT_89807_f_5.1_NKp4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>94.855</v>
+      </c>
+      <c r="D19" t="n">
+        <v>68.819</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>done - gcOP_WT_89807_f_5.1_NKp46_IB4 2.t</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>83.333</v>
+      </c>
+      <c r="D20" t="n">
+        <v>47.565</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>done - gcOP_WT_89807_f_5.1_NKp46_IB4 3.t</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>64</v>
+      </c>
+      <c r="D21" t="n">
+        <v>40.039</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>done - gcOP_WT_89807_f_5.1_NKp46_IB4 4.t</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>82.456</v>
+      </c>
+      <c r="D22" t="n">
+        <v>58.27</v>
       </c>
     </row>
   </sheetData>
